--- a/artfynd/A 25010-2026 artfynd.xlsx
+++ b/artfynd/A 25010-2026 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -803,53 +803,64 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134138517</v>
+        <v>134138542</v>
       </c>
       <c r="B3" t="n">
-        <v>8449</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579088</v>
+        <v>579080</v>
       </c>
       <c r="R3" t="n">
-        <v>6390199</v>
+        <v>6390373</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,11 +900,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår på stående död björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +908,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,64 +926,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134138542</v>
+        <v>134138517</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579080</v>
+        <v>579088</v>
       </c>
       <c r="R4" t="n">
-        <v>6390373</v>
+        <v>6390199</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,6 +1012,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår på stående död björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,6 +1025,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
